--- a/data/safco_full/products.xlsx
+++ b/data/safco_full/products.xlsx
@@ -572,6 +572,18 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Soft-Fit&amp;trade; powder-free nitrile exam gloves.
+Textured whole hand finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 3.1 mils; at fingertip 3.9 mils;&amp;nbsp;&amp;plusmn; 1.2
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>{}</t>
@@ -594,12 +606,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.055317+00:00</t>
+          <t>2026-06-27T05:42:17.688881+00:00</t>
         </is>
       </c>
     </row>
@@ -657,6 +669,18 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Soft-Fit&amp;trade; powder-free nitrile exam gloves.
+The Alasta Aloe nitrile exam gloves are a great choice for those who care for their hands. Experience the power of certified organic aloe, skin friendly design, and the Soft Fit&amp;trade; thin nitrile formulation. When you need nitrile gloves but want the comfort and performance of latex.
+Organic aloe provides soothing benefit to dry, irritated skin
+Skin friendly nitrile formulation lowers risk of developing contact dermatitis
+Glides on damp hands easily
+Thin design delivers increased touch sensitivity
+Cool green color
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>{}</t>
@@ -679,12 +703,12 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.058069+00:00</t>
+          <t>2026-06-27T05:42:17.694512+00:00</t>
         </is>
       </c>
     </row>
@@ -742,6 +766,13 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Make glove changes faster and easier with Alasta® PRO nitrile dental exam gloves, featuring innovative Glide Assist™ technology that helps you slide into gloves effortlessly — even with damp hands. Designed for dental professionals, the Soft Fit™ formulation provides a comfortable, form-fitting feel that enhances dexterity during procedures.
+The professional medical blue color offers a clean, clinical look that complements any operatory setting. Alasta® PRO gloves are fentanyl-tested and chemo-approved, ensuring trusted protection for use in high-risk or clinical dental environments.
+Each box contains 200 premium nitrile gloves, offering exceptional value and efficiency for busy dental practices.</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>{}</t>
@@ -764,12 +795,12 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.060361+00:00</t>
+          <t>2026-06-27T05:42:17.699550+00:00</t>
         </is>
       </c>
     </row>
@@ -827,6 +858,12 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Pink for a cause: for every case sold, DASH® Medical donates &amp;nbsp;$1 to The American Cancer SocietyTextured fingertip finishBeaded cuffAmbidextrousPink colorTested for use with chemotherapy drugsThickness: at palm 2.8 mils; at fingertips 3.9 mils100 gloves per boxOrder 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>{}</t>
@@ -849,12 +886,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.062842+00:00</t>
+          <t>2026-06-27T05:42:17.704682+00:00</t>
         </is>
       </c>
     </row>
@@ -912,6 +949,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Soft fit gloves with a textured finish for comfort and control.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+White color
+Thickness: at palm 3.1 mils; at fingertip 3.9 mils
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>{}</t>
@@ -934,12 +985,12 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.065285+00:00</t>
+          <t>2026-06-27T05:42:17.709908+00:00</t>
         </is>
       </c>
     </row>
@@ -997,6 +1048,22 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Coated on the inside with soothing aloe to help moisturize and soften your hands while working. The gloves are fully textured, providing a firm grip.
+Textured whole hand finish
+Powder-free
+Beaded cuff
+Chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+Aloe coated
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1019,12 +1086,12 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.067680+00:00</t>
+          <t>2026-06-27T05:42:17.715024+00:00</t>
         </is>
       </c>
     </row>
@@ -1082,6 +1149,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Natural form-fitting gloves coated with lanolin and Vitamin E.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Aqua color
+Thickness: at palm 3.2 mils; at fingertips 4.0 mils
+200 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1104,12 +1185,12 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.070026+00:00</t>
+          <t>2026-06-27T05:42:17.720077+00:00</t>
         </is>
       </c>
     </row>
@@ -1167,6 +1248,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Powder-free&amp;nbsp;chloroprene&amp;nbsp;examination gloves.
+Combines the comfort of latex and the strength of nitrile.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Aqua blue color
+Thickness: at palm 2.8 mils; at fingertip3.5 mils; &amp;plusmn;0.8
+200 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1189,12 +1283,12 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.072736+00:00</t>
+          <t>2026-06-27T05:42:17.725284+00:00</t>
         </is>
       </c>
     </row>
@@ -1252,6 +1346,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Ultra-thin with a silky, snug fit. Easy to don.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Blue
+Thickness: at palm 2.8mils; at fingertips 3.1 mils
+300 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1274,12 +1383,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.075246+00:00</t>
+          <t>2026-06-27T05:42:17.730401+00:00</t>
         </is>
       </c>
     </row>
@@ -1337,6 +1446,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Soft nitrile formulation with a high contrast black satin finish.&amp;nbsp;
+Textured full finger finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Black color
+Thickness: at palm 3.2 mils; at fingertip 4.0 mils
+200 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1359,12 +1482,12 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.077738+00:00</t>
+          <t>2026-06-27T05:42:17.735326+00:00</t>
         </is>
       </c>
     </row>
@@ -1422,6 +1545,22 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>&amp;lt;p&amp;gt;&amp;lt;em&amp;gt;Powder-free nitrile&amp;amp;nbsp;exam gloves.&amp;lt;/em&amp;gt;&amp;lt;/p&amp;gt;
+&amp;lt;p&amp;gt;Thinner and more&amp;amp;nbsp;flexible than standard&amp;amp;nbsp;nitrile.&amp;lt;/p&amp;gt;
+&amp;lt;ul&amp;gt;
+&amp;lt;li&amp;gt;Textured fingertip finish&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Beaded cuff&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Chlorinated&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Ambidextrous&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Purple color&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Thickness: at palm 2.0 mils; at fingertips 3.0 mils&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;300 gloves per box (270 for x-large)&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Order 10 boxes&amp;amp;nbsp;to purchase a case&amp;lt;/li&amp;gt;
+&amp;lt;/ul&amp;gt;</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1444,12 +1583,12 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.080113+00:00</t>
+          <t>2026-06-27T05:42:17.740571+00:00</t>
         </is>
       </c>
     </row>
@@ -1507,6 +1646,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile&amp;nbsp;exam gloves.
+Ultra-stretch nitrile.
+Textured fingertip finish
+Polymer coated for easy donning
+Beaded cuff
+Chlorinated
+Ambidextrous
+Pink color
+Thickness: at palm 2.5 mils; at fingertips 2.7 mils
+200 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1529,12 +1683,12 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.082620+00:00</t>
+          <t>2026-06-27T05:42:17.745539+00:00</t>
         </is>
       </c>
     </row>
@@ -1592,6 +1746,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Nitrile powder-free exam gloves.
+Maximum strength and durability.
+Fully-textured finish for improved grip
+Beaded cuff
+Chlorinated
+Ambidextrous
+Black color
+Thickness: at palm 5.0 mils; at fingertips 6.0 mils
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1614,12 +1782,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.085332+00:00</t>
+          <t>2026-06-27T05:42:17.750807+00:00</t>
         </is>
       </c>
     </row>
@@ -1677,6 +1845,22 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+&amp;nbsp;
+Premium quality.
+Honeycomb textured fingertips&amp;nbsp;and palms
+Beaded cuff
+Non-Chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+White color
+Polymer coated for easy donning
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1699,12 +1883,12 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.088014+00:00</t>
+          <t>2026-06-27T05:42:17.756015+00:00</t>
         </is>
       </c>
     </row>
@@ -1762,6 +1946,22 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+&amp;nbsp;
+Ultra-thin for ultimate comfort.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Teal green color
+Polymer coated for easy donning
+Thickness: at palm 2.5 mils; at fingertip 3.5 mils
+200 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1784,12 +1984,12 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.090551+00:00</t>
+          <t>2026-06-27T05:42:17.761221+00:00</t>
         </is>
       </c>
     </row>
@@ -1847,6 +2047,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Nitrile powder-free exam gloves.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 4.0 mils; at fingertip 5.2 mils;&amp;nbsp;&amp;plusmn; 1.2
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1869,12 +2082,12 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.092794+00:00</t>
+          <t>2026-06-27T05:42:17.766245+00:00</t>
         </is>
       </c>
     </row>
@@ -1932,6 +2145,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves with a peppermint scent.
+Honeycomb textured fingertips and palms
+Beaded cuff
+Non-Chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Green color
+Polymer coated for easy donning
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1954,12 +2181,12 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.095025+00:00</t>
+          <t>2026-06-27T05:42:17.771426+00:00</t>
         </is>
       </c>
     </row>
@@ -2017,6 +2244,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Nitrile powder-free exam gloves.
+Ultra-comfort nitrile formulation.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Indigo blue color
+Thickness: at palm 2.2 mils; at fingertips 3.2 mils
+300 gloves per box (270 for x-large)
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2039,12 +2280,12 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.097486+00:00</t>
+          <t>2026-06-27T05:42:17.776877+00:00</t>
         </is>
       </c>
     </row>
@@ -2102,6 +2343,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Nitrile powder-free exam gloves
+The same high tactility and lightweight comfort of Aurelia Sonic, but in a smaller count box to complement today&amp;rsquo;s more dynamic PPE environment.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Indigo blue color
+Thickness: at palm 2.2 mils; at fingertips 3.2 mils
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2124,12 +2379,12 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.100039+00:00</t>
+          <t>2026-06-27T05:42:17.782114+00:00</t>
         </is>
       </c>
     </row>
@@ -2187,6 +2442,22 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+&amp;nbsp;
+Ultra-thin formulation for superior tactile sensitivity.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Blue color
+Polymer coated for easy donning
+Thickness: at palm 3.0 mils; at fingertip 3.8 mils
+200 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2209,12 +2480,12 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.102677+00:00</t>
+          <t>2026-06-27T05:42:17.787416+00:00</t>
         </is>
       </c>
     </row>
@@ -2272,6 +2543,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Micro-textured finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2294,12 +2578,12 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.105024+00:00</t>
+          <t>2026-06-27T05:42:17.792902+00:00</t>
         </is>
       </c>
     </row>
@@ -2357,6 +2641,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Natural, form-fitting gloves coated with lanolin and Vitamin E.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Aqua color
+Thickness: at palm 3.2 mils; at fingertips 4.0 mils
+300 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2379,12 +2678,12 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.107531+00:00</t>
+          <t>2026-06-27T05:42:17.797884+00:00</t>
         </is>
       </c>
     </row>
@@ -2442,6 +2741,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Smooth polymer interior coating aids in both moist and dry donning.
+Micro-textured whole hand finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+Polymer coating for easy donning
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2464,12 +2778,12 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.110082+00:00</t>
+          <t>2026-06-27T05:42:17.803002+00:00</t>
         </is>
       </c>
     </row>
@@ -2527,6 +2841,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Powder-free&amp;nbsp;chloroprene&amp;nbsp;examination gloves.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Green color
+Polymer coated for easy donning
+Thickness: at palm 3.2 mils; at fingertip 3.4 mils; &amp;plusmn;0.2
+200 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2549,12 +2876,12 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.112594+00:00</t>
+          <t>2026-06-27T05:42:17.809531+00:00</t>
         </is>
       </c>
     </row>
@@ -2612,6 +2939,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Ultrasoft nitrile formulation for latex-like comfort.
+Textured fingertip finish.
+Beaded cuff.
+Non-chlorinated.
+Ambidextrous.
+Blue color.
+Thickness: at palm 3 mils; at fingertip 4 mils; ± 0.8.
+100 gloves per box.
+Order 10 boxes to purchase a case.</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2634,12 +2975,12 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.115204+00:00</t>
+          <t>2026-06-27T05:42:17.814621+00:00</t>
         </is>
       </c>
     </row>
@@ -2697,6 +3038,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Ultrathin, ultrasoft formulation for latex-like comfort and tactile sensitivity.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+White color
+Thickness: at palm 2.5 mils; at fingertip 3 mils
+200 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2719,12 +3074,12 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.117669+00:00</t>
+          <t>2026-06-27T05:42:17.819669+00:00</t>
         </is>
       </c>
     </row>
@@ -2782,6 +3137,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile&amp;nbsp;exam gloves.
+Super soft and stretchy for comfortable extended wear.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Cobalt blue color
+Thickness: at palm 2.0 mils; at fingertips 2.0 mils
+300 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2804,12 +3173,12 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.120192+00:00</t>
+          <t>2026-06-27T05:42:17.824855+00:00</t>
         </is>
       </c>
     </row>
@@ -2867,6 +3236,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Ultra tactile and donning ease.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Blue color
+Thickness: at palm 2.0 mils; at fingertip 3.5 mils
+350 gloves per box (Large size 300 gloves per box)
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2889,12 +3271,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.122588+00:00</t>
+          <t>2026-06-27T05:42:17.830174+00:00</t>
         </is>
       </c>
     </row>
@@ -2952,6 +3334,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>BioNitrile gloves are made with advanced biodegradable materials that break down 90% in less than 1.5 years. This reduces permanent waste and means less greenhouse gas emissions.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Blue color
+Thickness at palm 2.0 mils
+Thickness at fingertip 2.2 mils
+300 gloves per box (250 size XL)
+Order 10 boxes to purchase a case.</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>{}</t>
@@ -2974,12 +3369,12 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.124991+00:00</t>
+          <t>2026-06-27T05:42:17.835444+00:00</t>
         </is>
       </c>
     </row>
@@ -3037,6 +3432,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Proprietary inner coating helps gloves glide on damp hands easily.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Black color
+Polymer coated
+Thickness: at palm 2.8 mils; at fingertip 3.9 mils
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3059,12 +3467,12 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.127469+00:00</t>
+          <t>2026-06-27T05:42:17.840982+00:00</t>
         </is>
       </c>
     </row>
@@ -3122,6 +3530,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Textured whole hand finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+No protein claim
+Natural color
+Polymer coating for easy donning
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3144,12 +3566,12 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.130158+00:00</t>
+          <t>2026-06-27T05:42:17.846124+00:00</t>
         </is>
       </c>
     </row>
@@ -3207,6 +3629,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Exceptionally strong and flexible formulation prevents tearing, especially while donning.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Black
+Thickness: at palm 2.0mils; at fingertips 2.7mils
+300 gloves per box (250 for x-large)
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3229,12 +3664,12 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.132642+00:00</t>
+          <t>2026-06-27T05:42:17.851273+00:00</t>
         </is>
       </c>
     </row>
@@ -3292,6 +3727,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+&amp;nbsp;
+Distinct black color to minimize visible stains.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Black&amp;nbsp;color
+Thickness: at palm 3.2 mils; at fingertip 3.4 mils
+200 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3314,12 +3763,12 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.134933+00:00</t>
+          <t>2026-06-27T05:42:17.856464+00:00</t>
         </is>
       </c>
     </row>
@@ -3377,9 +3826,14 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Compac™ By The Cuff® Nitrile Powder Free Exam Gloves feature innovative dispensing technology designed to reduce cross-contamination, minimize glove waste, and improve operatory efficiency.</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Brand": "Cranberry® Compac", "Product Type": "Nitrile Exam Gloves", "Material": "Powder-free nitrile", "Thickness": "Approximately 2.2–2.5 mil", "Texture": "Fingertip textured", "Sterility": "Non-sterile", "Color": "Black", "Packaging": "100 gloves per bag", "Available Sizes": "XS, S, M, L, XL", "Use Case": "Dental and clinical examination procedures"}</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3399,12 +3853,12 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.137324+00:00</t>
+          <t>2026-06-27T05:42:17.861641+00:00</t>
         </is>
       </c>
     </row>
@@ -3462,6 +3916,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Good tactile sensitivity with maximum puncture resistance.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 4.3 mils; at fingertip 5 mils;&amp;nbsp;&amp;plusmn; 0.8
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3484,12 +3952,12 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.139659+00:00</t>
+          <t>2026-06-27T05:42:17.866808+00:00</t>
         </is>
       </c>
     </row>
@@ -3547,6 +4015,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Coated with Vitamin E and Lanolin.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+White color
+Thickness: at palm 4.3 mils; at fingertip 5.1 mils;&amp;nbsp;&amp;plusmn; 1.2
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3569,12 +4051,12 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.141963+00:00</t>
+          <t>2026-06-27T05:42:17.872004+00:00</t>
         </is>
       </c>
     </row>
@@ -3632,6 +4114,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam glove with lanolin and Vitamin E.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Blue color
+Vitamin E and lanolin coated
+Thickness: at palm 3.5 mils; at fingertip 3.8 mils
+200 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3654,12 +4150,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.144453+00:00</t>
+          <t>2026-06-27T05:42:17.877267+00:00</t>
         </is>
       </c>
     </row>
@@ -3717,6 +4213,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Hand fitted to alleviate stress and fatigue during extended wear.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Left/Right hand specific
+White color
+Thickness: at palm 3.5 mils; at fingertip 4 mils;&amp;nbsp;&amp;plusmn; 0.8
+100 gloves per box (50 left/right pairs)
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3739,12 +4249,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.146744+00:00</t>
+          <t>2026-06-27T05:42:17.882501+00:00</t>
         </is>
       </c>
     </row>
@@ -3802,6 +4312,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Mild citrus-peppermint scent, and coated with lanolin and Vitamin E to improve skin health.&amp;nbsp;
+Textured whole hand finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Wintergreen color
+Vitamin E and lanolin coated
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3824,12 +4349,12 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.149188+00:00</t>
+          <t>2026-06-27T05:42:17.887907+00:00</t>
         </is>
       </c>
     </row>
@@ -3887,6 +4412,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Latex powder-free sterile surgical gloves
+Textured finish
+Beaded cuff
+Right/left hand specific
+Natural latex&amp;nbsp;color
+Thickness: at palm 7.5 mils; at fingertips: 8.0 mils
+Length: 11.6" (295mm)
+50 pairs (100 gloves)&amp;nbsp;gloves per box
+4 boxes in a case</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3909,12 +4447,12 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.151640+00:00</t>
+          <t>2026-06-27T05:42:17.892977+00:00</t>
         </is>
       </c>
     </row>
@@ -3972,6 +4510,18 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Latex powder-free sterile surgical gloves.
+Textured finish
+Beaded cuff
+Right/left hand specific
+Polymer coated for fast and easy donning
+Natural latex color
+50 pairs (100 gloves) per box
+4 boxes in a case</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>{}</t>
@@ -3994,12 +4544,12 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.153893+00:00</t>
+          <t>2026-06-27T05:42:17.898069+00:00</t>
         </is>
       </c>
     </row>
@@ -4057,6 +4607,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Essential Textured Powder-free exam gloves are designed to help reduce your sensitivity to latex. All the benefits of the original Essential Powder Free, with the added feature of a textured finish for superior gripping ability. Super stretchy with excellent resistance to tears.
+Material: Latex
+Powder-free
+Thickness: 5.5 mil
+Textured fingertips
+Fit: Ambidextrous
+Length: 9.5"
+Color: Off White
+Available in 3 Sizes: TPFS&amp;nbsp;small, TPFM&amp;nbsp;medium, TPFL&amp;nbsp;large
+Case Pack: 100 gloves per box, 10 boxes per case</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4079,12 +4643,12 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.156199+00:00</t>
+          <t>2026-06-27T05:42:17.903197+00:00</t>
         </is>
       </c>
     </row>
@@ -4142,6 +4706,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile&amp;nbsp;exam gloves.
+Strong and soft comfort&amp;nbsp;during extended wear.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Royal blue color
+Polymer coated for easy donning
+Thickness: at palm 2.0 mils; at fingertip 2.0 mils
+300 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4164,12 +4743,12 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.158656+00:00</t>
+          <t>2026-06-27T05:42:17.908313+00:00</t>
         </is>
       </c>
     </row>
@@ -4227,6 +4806,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Powder-free chloroprene examination gloves.
+Fingertip textured
+Beaded cuff
+Ambidextrous
+Chloroprene (Neoprene)
+Green color
+Polymer coated for easy donning
+Thickness: at palm 3.0 mils; at fingertip 3.5 mils
+200 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4249,12 +4842,12 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.161206+00:00</t>
+          <t>2026-06-27T05:42:17.913768+00:00</t>
         </is>
       </c>
     </row>
@@ -4312,6 +4905,17 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Cobalt color
+Thickness: at palm 1.9 mils; at fingertip 3.1 mils
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4334,12 +4938,12 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.163764+00:00</t>
+          <t>2026-06-27T05:42:17.919073+00:00</t>
         </is>
       </c>
     </row>
@@ -4397,6 +5001,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 3.5 mils; at fingertip 4.7 mils
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4419,12 +5036,12 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.166190+00:00</t>
+          <t>2026-06-27T05:42:17.923991+00:00</t>
         </is>
       </c>
     </row>
@@ -4482,6 +5099,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>HALYARD* Black Nitrile Exam Gloves deliver dependable protection and professional performance for dental professionals. Perfect for clinical and hygiene procedures, these nitrile gloves provide excellent tactile sensitivity and a secure grip with textured fingertips for confident instrument handling. The sleek black color conceals stains, maintaining a clean, modern look in any dental setting. Each box contains 100 gloves in a SMARTPULL* Dispenser designed to reduce waste, improve efficiency, and save valuable operatory space.</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4504,12 +5126,12 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.168621+00:00</t>
+          <t>2026-06-27T05:42:17.928931+00:00</t>
         </is>
       </c>
     </row>
@@ -4567,6 +5189,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Nitrile flock-lined utility gloves.
+Puncture resistant gloves&amp;nbsp;protect hands from harsh&amp;nbsp;chemicals, solvents,&amp;nbsp;and oils. Can be steam&amp;nbsp;autoclaved up to five times.
+Textured whole hand finish
+Flat cuff
+Non-chlorinated
+Left/right-hand fitted
+Lilac color
+Thickness: 0.38mm
+3 pairs per box</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4589,12 +5224,12 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.171251+00:00</t>
+          <t>2026-06-27T05:42:17.934213+00:00</t>
         </is>
       </c>
     </row>
@@ -4652,6 +5287,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+InSoft&amp;trade; formulation for increased comfort and minimal hand fatigue.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Aegean blue color
+Thickness: at palm 2.0 mils; at fingertip 2.3 mils
+300 gloves per box (250 for x-large)
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4674,12 +5323,12 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.173894+00:00</t>
+          <t>2026-06-27T05:42:17.939304+00:00</t>
         </is>
       </c>
     </row>
@@ -4737,6 +5386,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Soft and strong; one of the thinnest nitrile gloves on the market. Thicker and longer cuff!
+Textured fingertips
+Beaded cuff
+Low dermatitis potential
+Ambidextrous
+Lavender color
+Thickness: at palm 2.0 mils; at fingertip 2.8 mils
+250 gloves per box (230 for x-large)
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4759,12 +5422,12 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.176748+00:00</t>
+          <t>2026-06-27T05:42:17.944246+00:00</t>
         </is>
       </c>
     </row>
@@ -4822,6 +5485,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Coated&amp;nbsp;with a blend of lanolin and Vitamin E to maximize moisture retention, and for easy donning.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Azure blue color
+Thickness: at palm 2.5 mils; at fingertip 2.6 mils
+300 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4844,12 +5521,12 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.179362+00:00</t>
+          <t>2026-06-27T05:42:17.949425+00:00</t>
         </is>
       </c>
     </row>
@@ -4907,6 +5584,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Powder-free Neoprene&amp;nbsp;(polychloroprene)&amp;nbsp;exam gloves.
+Textured fingertips finish&amp;nbsp;
+Beaded cuff&amp;nbsp;
+Ambidextrous
+Neoprene&amp;nbsp;
+Green color
+Polymer coated for easy donning&amp;nbsp;
+Thickness: at palm 5.1 mils; at fingertip 6.3 mils&amp;nbsp;
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>{}</t>
@@ -4929,12 +5620,12 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.181931+00:00</t>
+          <t>2026-06-27T05:42:17.954550+00:00</t>
         </is>
       </c>
     </row>
@@ -4992,6 +5683,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Comfortable and reliable protection with a low dermatits potential. Made without sulfur-based chemical accelerants for tactility and to help prevent allergic reactions.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Blue color
+Thickness: at palm 2.8 mils; at fingertip 3.9 mils
+200 gloves per box (X-large 180 gloves per box)
+Order 10 boxes to purchase a case
+Tested for use with chemotherapy drugs</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5014,12 +5719,12 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.184461+00:00</t>
+          <t>2026-06-27T05:42:17.959601+00:00</t>
         </is>
       </c>
     </row>
@@ -5077,6 +5782,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Made from a durable and soft nitrile formulation manufactured without chemical accelerators, helping to protect the user from allergies.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Pink color
+Thickness: at palm 3.1 mils; at fingertip 5.5 mils
+100 gloves per box
+Order 10 boxes to purchase a case
+Tested for use with chemotherapy drugs</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5099,12 +5818,12 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.187092+00:00</t>
+          <t>2026-06-27T05:42:17.964795+00:00</t>
         </is>
       </c>
     </row>
@@ -5162,6 +5881,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Advanced stretch formulation for ultimate comfort and fit.
+Textured fingertips finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 2.4 mils; at fingertip 3.1 mils
+200 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5184,12 +5917,12 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.189629+00:00</t>
+          <t>2026-06-27T05:42:17.969881+00:00</t>
         </is>
       </c>
     </row>
@@ -5247,6 +5980,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Powder-free, form-fitting, latex exam gloves.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5269,12 +6015,12 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.219865+00:00</t>
+          <t>2026-06-27T05:42:18.039079+00:00</t>
         </is>
       </c>
     </row>
@@ -5332,6 +6078,18 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.&amp;nbsp;
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Blue color
+Thickness: at palm 2.8 mils; at fingertip 4.3 mils
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5354,12 +6112,12 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.191999+00:00</t>
+          <t>2026-06-27T05:42:17.974917+00:00</t>
         </is>
       </c>
     </row>
@@ -5417,6 +6175,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.&amp;nbsp;
+Medical grade exam glove.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+Polymer coated for easy donning
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5439,12 +6212,12 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.194172+00:00</t>
+          <t>2026-06-27T05:42:17.980094+00:00</t>
         </is>
       </c>
     </row>
@@ -5502,6 +6275,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+Polymer coating for easy donning
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5524,12 +6311,12 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.196537+00:00</t>
+          <t>2026-06-27T05:42:17.985172+00:00</t>
         </is>
       </c>
     </row>
@@ -5587,6 +6374,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Blue color
+Polymer coated for easy donning
+Thickness: at palm 3.9 mils; at fingertip 5.5 mils
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5609,12 +6410,12 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.198718+00:00</t>
+          <t>2026-06-27T05:42:17.990355+00:00</t>
         </is>
       </c>
     </row>
@@ -5672,6 +6473,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Black color
+Thickness: at palm 4.7 mils; at fingertip 6.3 mils
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5694,12 +6508,12 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.201143+00:00</t>
+          <t>2026-06-27T05:42:17.995707+00:00</t>
         </is>
       </c>
     </row>
@@ -5757,6 +6571,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+ERGOFORM technology reduces muscle strain and improves comfort
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Black color
+Thickness: at palm 2.8 mils; at fingertip 4.3 mils
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5779,12 +6606,12 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.203233+00:00</t>
+          <t>2026-06-27T05:42:18.001494+00:00</t>
         </is>
       </c>
     </row>
@@ -5842,6 +6669,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Powder-free chloroprene examination gloves.
+Textured whole hand finish
+Beaded cuff
+Ambidextrous
+Chloroprene
+Green color
+Polymer coated for easy donning
+Thickness: at palm 5.1&amp;nbsp; mils; at fingertip 6.7 mils
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5864,12 +6705,12 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.207864+00:00</t>
+          <t>2026-06-27T05:42:18.011981+00:00</t>
         </is>
       </c>
     </row>
@@ -5927,6 +6768,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Powder-free chloroprene examination gloves.
+Features HYDRASOFT&amp;trade; technology that provides 2x more moisture retention.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Chloroprene (neoprene)
+Green color
+Polymer coated for easy donning
+Thickness: at palm 2.8&amp;nbsp; mils; at fingertip 3.5 mils
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t>{}</t>
@@ -5949,12 +6805,12 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.210901+00:00</t>
+          <t>2026-06-27T05:42:18.017634+00:00</t>
         </is>
       </c>
     </row>
@@ -6012,6 +6868,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Powder-free chloroprene exam gloves.
+Thin, ultralight, neoprene exam glove designed for heightened tactile sensitivity. US Ergonomics certified for exceptional wet grip.
+Features ERGOFORM&amp;trade; technology to reduce stress on joints, ligaments, and tendons in the hands and wrists.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Green color
+Thickness: at palm 2.8 mils; at fingertip 3.5 mils
+200 gloves per box (180 per box in size XL)
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6034,12 +6904,12 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.205589+00:00</t>
+          <t>2026-06-27T05:42:18.006672+00:00</t>
         </is>
       </c>
     </row>
@@ -6097,6 +6967,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Patented Hydrasoft&amp;trade; technology allows skin to retain more moisture.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+White color
+Thickness: at palm 2.6 mils; at fingertip 3.7 mils
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6119,12 +7003,12 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.213163+00:00</t>
+          <t>2026-06-27T05:42:18.022883+00:00</t>
         </is>
       </c>
     </row>
@@ -6182,6 +7066,24 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+&amp;nbsp;
+Ultra-soft and form fitting.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Cobalt blue color
+Thickness: at palm 2.0 mils; at fingertip 3.1 mils
+300 gloves per box (250 for x-large)
+Order 10 boxes&amp;nbsp;to purchase a case
+&amp;nbsp;
+&amp;nbsp;
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6204,12 +7106,12 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.215538+00:00</t>
+          <t>2026-06-27T05:42:18.028184+00:00</t>
         </is>
       </c>
     </row>
@@ -6267,6 +7169,23 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile examination gloves.
+&amp;nbsp;
+Microflex XCEED gloves are manufactured without sulfur-based chemical accelerants for low dermatitis potential and prevent instances of Type 1 latex allergies and Type IV chemical allergic reactions. Boasts stronger formulation to protect against rips and tears while keeping the same tactile sensitivity. Designed with proprietary ergonomic design technology to support musculoskeletal health and increase worker productivity. With low 0.65 AQL, these gloves offer advanced barrier integrity.
+&amp;nbsp;
+The 1st exam glove certified as ergonomic by US Ergo.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 2.8 mils; at fingertip 3.5 mils
+250 gloves per box (230 for x-large)
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6289,12 +7208,12 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.217737+00:00</t>
+          <t>2026-06-27T05:42:18.033478+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,6 +7271,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Powder-free&amp;nbsp;chloroprene&amp;nbsp;exam gloves.
+Exceptional tactile&amp;nbsp;sensitivity. Excellent wet and dry grip. Stretchy soft comfort.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Chloroprene
+Polymer coated for easy donning
+Green color
+Thickness: at palm 3.9 mils; at fingertip 5.1 mils
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6374,12 +7308,12 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.222123+00:00</t>
+          <t>2026-06-27T05:42:18.044363+00:00</t>
         </is>
       </c>
     </row>
@@ -6437,6 +7371,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+White color
+Thickness: at palm 3.1 mils; at fingertip 3.9 mils;&amp;nbsp;&amp;plusmn; 0.8
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6459,12 +7406,12 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.226956+00:00</t>
+          <t>2026-06-27T05:42:18.060326+00:00</t>
         </is>
       </c>
     </row>
@@ -6522,6 +7469,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Nitrile powder-free sterile surgical gloves
+Textured finish
+Beaded cuff
+Right/left hand specific
+White color
+Thickness at fingertips: 7.0 mils
+Length: 12"
+50 pairs (100 gloves) per box
+4 boxes in a case</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6544,12 +7504,12 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.224461+00:00</t>
+          <t>2026-06-27T05:42:18.054959+00:00</t>
         </is>
       </c>
     </row>
@@ -6607,6 +7567,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Powder-free vinyl examination gloves.
+Soft, form fitting gloves designed to retain the superior elongation properties of latex normally absent from vinyl gloves.
+Smooth finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Gloves are white
+Thickness: at palm 3.2 mils; at fingertip 2.3 mils
+100 gloves per box
+10 boxes in a case</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6629,12 +7603,12 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.229442+00:00</t>
+          <t>2026-06-27T05:42:18.065536+00:00</t>
         </is>
       </c>
     </row>
@@ -6687,6 +7661,18 @@
           <t>out_of_stock</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Powder-free vinyl exam gloves.
+Smooth finish
+Beaded cuff
+Ambidexterous
+Vinyl
+White color
+100 gloves per box
+10 boxes in a case</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6709,12 +7695,12 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.231548+00:00</t>
+          <t>2026-06-27T05:42:18.070853+00:00</t>
         </is>
       </c>
     </row>
@@ -6772,6 +7758,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Powder-free chloroprene examination gloves.
+Polychlorprene exam gloves combine the softness of latex with the strength of nitrile for reliable protection without sacrificing comfort or dexterity.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Emerald green color
+Thickness: at palm 3.1 mils; at fingertip 4 mils
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6794,12 +7793,12 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.233706+00:00</t>
+          <t>2026-06-27T05:42:18.075974+00:00</t>
         </is>
       </c>
     </row>
@@ -6857,6 +7856,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Latex powder-free exam gloves.
+Multi-layer latex glove that combines the elasticity of latex and the strength of copolymers. Fusion bonding protects against cracking and peeling in normal use.
+Textured fingertip finish
+Beaded cuff
+Polymer coated
+Ambidextrous
+Natural white color
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6879,12 +7891,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.235977+00:00</t>
+          <t>2026-06-27T05:42:18.081187+00:00</t>
         </is>
       </c>
     </row>
@@ -6942,6 +7954,22 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Protect hands and the environment with a biodegradable single-use exam glove that combines performance, durability and tactile sensitivity for critical tasks. EcoTek&amp;reg; Biodegradability Technology accelerates landfill breakdown without any performance loss.&amp;nbsp;
+Tear-resistant beaded cuff&amp;nbsp;
+Fully textured
+Consistent thickness for greater dexterity and tactile sensitivity
+Silicone-free for critical environments
+Clean processing technology reduces potential skin irritation
+Black color
+5.0 mil. thickness
+1.5 AQL exceeds laboratory standards
+100 gloves per box
+Order 10 boxes to purchase a case.</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>{}</t>
@@ -6964,12 +7992,12 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.238031+00:00</t>
+          <t>2026-06-27T05:42:18.086469+00:00</t>
         </is>
       </c>
     </row>
@@ -7027,6 +8055,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Polymer bonded interior for easy donning. Slightly thinner for incredible tactile sensitivity and comfort.
+Textured whole hand finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+White color
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7049,12 +8090,12 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.240244+00:00</t>
+          <t>2026-06-27T05:42:18.091691+00:00</t>
         </is>
       </c>
     </row>
@@ -7112,6 +8153,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Thinner, but stronger and more elastic than normal nitrile gloves. The softer, more relaxed formulation is ideal for its ability to reduce muscle fatigue.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 2.5 mils; at fingertip 3.0 mils.
+300 gloves per box
+10 boxes in a case</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7134,12 +8189,12 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.244919+00:00</t>
+          <t>2026-06-27T05:42:18.102045+00:00</t>
         </is>
       </c>
     </row>
@@ -7197,6 +8252,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+&amp;nbsp;
+Finish provides superior gripping ability. Excellent donning properties and comfort.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7219,12 +8289,12 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.242818+00:00</t>
+          <t>2026-06-27T05:42:18.096739+00:00</t>
         </is>
       </c>
     </row>
@@ -7282,6 +8352,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile&amp;nbsp;exam gloves.
+Textured fingertip finish
+Beaded cuff
+Lightly chlorinated
+Ambidextrous
+Dark lavender blue color
+Thickness: at palm 3.0mils; at fingertips 3.5 mils
+200 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7304,12 +8387,12 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.247069+00:00</t>
+          <t>2026-06-27T05:42:18.107202+00:00</t>
         </is>
       </c>
     </row>
@@ -7367,6 +8450,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Purple color
+Thickness: at palm 4.7 mils; at fingertip 5.9 mils
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7389,12 +8485,12 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.249248+00:00</t>
+          <t>2026-06-27T05:42:18.112345+00:00</t>
         </is>
       </c>
     </row>
@@ -7452,6 +8548,23 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+The soft and stretchy formulation of the Quantum Blue Nitrile Exam Glove provides for an exceptional fit and feel. Nonstick interior makes donning a breeze, even with damp hands. Micro-textured outer surface allows superior gripping of instruments. The super soft and stretchy formulation mimics the fit and feel of latex. Quantum Blue exam gloves are highly puncture and chemical resistant.
+Super soft and stretchy
+Non-stick inner surface
+Fit: Ambidextrous
+4.0 MIL thick
+Length: 9.5"
+Beaded cuff
+Micro-textured outer surface
+Color: Vibrant blue
+Industries: Dental, veterinarian, mortuary, cleaning, tattoo
+Case Pack: 100 gloves per box, 10 boxes per case
+Formerly called Cobalt Blue</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7474,12 +8587,12 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.251356+00:00</t>
+          <t>2026-06-27T05:42:18.117602+00:00</t>
         </is>
       </c>
     </row>
@@ -7537,6 +8650,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Unprecedented softness and comfort.
+Textured fingertip&amp;nbsp;finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Dark blue&amp;nbsp;color
+Thickness: at palm 2.0 mils; at fingertip 2.8&amp;nbsp;mils
+200 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7559,12 +8686,12 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.253996+00:00</t>
+          <t>2026-06-27T05:42:18.122851+00:00</t>
         </is>
       </c>
     </row>
@@ -7622,6 +8749,18 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Nitrile powder-free exam gloves.
+Unique nitrile formulation created for enhanced ease of use, softness, and fit. Improved fingertip texture offers superior handling and control.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Blue color
+Thickness: at palm 2.0 mils; at fingertip 2.8 mils
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7644,12 +8783,12 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.256538+00:00</t>
+          <t>2026-06-27T05:42:18.128335+00:00</t>
         </is>
       </c>
     </row>
@@ -7707,6 +8846,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Safco&amp;rsquo;s natural latex provides an ultra-soft feel with the&amp;nbsp;quality and value you&amp;rsquo;ve come to expect from Safco products.
+Whole-hand micro-textured finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural&amp;nbsp;latex white
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7729,12 +8882,12 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.258874+00:00</t>
+          <t>2026-06-27T05:42:18.133579+00:00</t>
         </is>
       </c>
     </row>
@@ -7792,6 +8945,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Powder-free chloroprene examination gloves.
+Similar feel and elasticity to that of latex without the risk of allergic reation to latex proteins. Provides supreme tactile sensitivity.
+Textured fingertip finish
+Beaded cuff
+Ambidextreous
+Green color
+Thickness: at palm 3.0 mils; at fingertips 3.5 mils
+200 gloves per box
+Order 10 boxes to purchase a case
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7814,12 +8981,12 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.261569+00:00</t>
+          <t>2026-06-27T05:42:18.138864+00:00</t>
         </is>
       </c>
     </row>
@@ -7877,6 +9044,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Soft, micro-textured formulation provides a more natural comfort and feel not typically found in other nitrile gloves. Easy-don formulation.
+Textured whole hand finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 4.3 mils; at fingertip 5.1 mils;&amp;nbsp;&amp;plusmn; 1.2
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7899,12 +9081,12 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.263919+00:00</t>
+          <t>2026-06-27T05:42:18.144186+00:00</t>
         </is>
       </c>
     </row>
@@ -7962,6 +9144,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Our strongest and thinnest nitrile glove yet. Designed to preserve the sensitivity you have come to expect from the Nitrilex line of gloves.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextreous
+Black color
+Polymer coated for easy donning
+Thickness: at palm 2.0 mils; at fingertip 2.3 mils
+200 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
           <t>{}</t>
@@ -7984,12 +9181,12 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.266141+00:00</t>
+          <t>2026-06-27T05:42:18.149685+00:00</t>
         </is>
       </c>
     </row>
@@ -8047,6 +9244,22 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Nitrilex Prevail preserves ultimate tactile sensitivity with the strength you have come to expect from our line of Nitrilex exam gloves.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Blue color
+Polymer coated for easy donning
+Thickness at palm 2.5 mils; at fingertips 3.0 mils
+300 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8069,12 +9282,12 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.268249+00:00</t>
+          <t>2026-06-27T05:42:18.154792+00:00</t>
         </is>
       </c>
     </row>
@@ -8132,6 +9345,22 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Our reliably strong and thin nitrile glove, but now with a colloidal oatmeal coating. This is specifically formulated to lock in moisture, giving your skin a chance to rehydrate from handwashing. Designed to soften your skin and soothe itching, our anti-inflammatory properties make our Safco Nitrilex Soothe perfect for clinicians with dry skin, returning your hands to their natural PH balance.&amp;nbsp;
+Made in Malaysia
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextreous
+Chemotherapy drug tested per ASTM D6978
+Robin Egg Blue color
+Moisturizing anti-irritant and anti-inflammatory colloidal oatmeal coated
+Thickness: at palm 2.5 mils; at fingertip 3.3 mils
+To purchase a full case, please order as qty of 10</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8154,12 +9383,12 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.270397+00:00</t>
+          <t>2026-06-27T05:42:18.159911+00:00</t>
         </is>
       </c>
     </row>
@@ -8217,6 +9446,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+A comfortable glove you can wear all day without fatigue. Designed to exceed your expectations in durability and comfort while maintaining tactile sensitivity. Features textured fingertips with the strength you have come to expect in our Nitrilex line of exam gloves. ASTM D6978 tested and approved for use with chemotherapy drugs.
+Textured fingertip finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 3.2 mils; at fingertip 3.5 mils
+300 gloves per box
+Order 10 boxes to purchase a case
+For full Dental Product Shopper review&amp;nbsp;click here.</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8239,12 +9483,12 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.272759+00:00</t>
+          <t>2026-06-27T05:42:18.165378+00:00</t>
         </is>
       </c>
     </row>
@@ -8302,6 +9546,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Ultra-soft and&amp;nbsp;form-fitting&amp;nbsp;with a textured&amp;nbsp;fingertip finish. &amp;nbsp;Gloves dispense easily, one by one.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Lavender blue color
+Thickness: at palm 3.2 mils; at fingertips 3.5 mils
+200 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8324,12 +9582,12 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.275113+00:00</t>
+          <t>2026-06-27T05:42:18.170910+00:00</t>
         </is>
       </c>
     </row>
@@ -8387,6 +9645,20 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Textured whole hand finish
+Beaded cuff
+Lightly chlorinated
+Ambidextrous
+50&amp;micro;g or less of latex protein
+Natural color
+Polymer coated for easy donning
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8409,12 +9681,12 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.277340+00:00</t>
+          <t>2026-06-27T05:42:18.176005+00:00</t>
         </is>
       </c>
     </row>
@@ -8472,6 +9744,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Coated with USP grade Lanolin and Vitamin E to minimize dry skin irritation associated with frequent hand washing.
+Textured whole hand finish
+Beaded cuff
+Lightly chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+Vitamin E and lanolin coated
+100 gloves per box
+Order 10 boxes to purchase a case</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8494,12 +9781,12 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.279503+00:00</t>
+          <t>2026-06-27T05:42:18.181301+00:00</t>
         </is>
       </c>
     </row>
@@ -8557,6 +9844,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Low Derma technology reduces the risk of skin irritation.
+Textured fingertip finish
+Beaded cuff
+Chlorinated
+Ambidextrous
+Matte blue color
+Thickness: at palm 2.5 mils; at fingertip 2.9 mils
+300 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8579,12 +9881,12 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.281692+00:00</t>
+          <t>2026-06-27T05:42:18.186647+00:00</t>
         </is>
       </c>
     </row>
@@ -8642,6 +9944,18 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Powder-free, latex-free, chloroprene examination gloves.
+Unrivaled wet grip, increased touch sensitivity, and silky smooth comfort. Chemotherapty drug rated.
+Textured fingertip finish
+Beaded cuff
+Ambidextrous
+Ocean blue color
+Thickness: at palm 2.4 mils; at fingertip 3.1 mils
+To purchase a full case, please order as qty of 10 boxes</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8664,12 +9978,12 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.284218+00:00</t>
+          <t>2026-06-27T05:42:18.191541+00:00</t>
         </is>
       </c>
     </row>
@@ -8727,6 +10041,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>SW Safety TrueForm Exam Glove TF-95RB 3.1 MIL&amp;nbsp;in&amp;nbsp;Royal Blue. Medical grade glove with textured fingertips and reinforced palm. Perfect for dental, medical applications as well as veterinarian and dairy.&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8749,12 +10068,12 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.286441+00:00</t>
+          <t>2026-06-27T05:42:18.196932+00:00</t>
         </is>
       </c>
     </row>
@@ -8812,6 +10131,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Powder-free latex exam gloves.
+Textured whole hand finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+50&amp;mu;g or less of latex protein
+Natural color
+100 gloves per box
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8834,12 +10166,12 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.288808+00:00</t>
+          <t>2026-06-27T05:42:18.202106+00:00</t>
         </is>
       </c>
     </row>
@@ -8897,6 +10229,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Three size options to hold 2, 3 or 4 glove boxes. 4" depth can accommodate virtually any size glove box on the market. Steel construction with baked-on white finish. Includes wall mounting hardware.&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
           <t>{}</t>
@@ -8919,12 +10256,12 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.291035+00:00</t>
+          <t>2026-06-27T05:42:18.207190+00:00</t>
         </is>
       </c>
     </row>
@@ -8982,6 +10319,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Powder-free nitrile exam gloves.
+Textured fingertip&amp;nbsp;finish
+Beaded cuff
+Non-chlorinated
+Ambidextrous
+Blue color
+Thickness: at palm 2.4 mils; at fingertip 3.2 mils
+100 gloves per box&amp;nbsp;
+Order 10 boxes&amp;nbsp;to purchase a case</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9004,12 +10354,12 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:52.293263+00:00</t>
+          <t>2026-06-27T05:42:18.212438+00:00</t>
         </is>
       </c>
     </row>
@@ -9067,6 +10417,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Hemostatic non-resorbable gauze. For&amp;nbsp;external use. Absorbs exudates such as blood or other bodily fluids. Easy to cut to any size or shape. Dispensed in individual&amp;nbsp;sterile pouches.</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9089,12 +10444,12 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.212395+00:00</t>
+          <t>2026-06-27T05:42:18.838799+00:00</t>
         </is>
       </c>
     </row>
@@ -9152,6 +10507,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Visible light cured periodontal dressing in a convenient syringe delivery system for direct placement onto the surgical site. Forms a firm, elastic covering. Translucent pink for superior esthetics. Tasteless.</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9174,12 +10534,12 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.214979+00:00</t>
+          <t>2026-06-27T05:42:18.843626+00:00</t>
         </is>
       </c>
     </row>
@@ -9237,6 +10597,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Non-eugenol surgical dressing and periodontal pack that has no burning sensation, no unpleasant taste, no disagreeable odor and offers proven protection to surgical sites. Extremely plastic and cohesive; ropes of any length or thickness can be formed. Sets with resilient,&amp;nbsp;non-brittle hardness.</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9259,12 +10624,12 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.217447+00:00</t>
+          <t>2026-06-27T05:42:18.848458+00:00</t>
         </is>
       </c>
     </row>
@@ -9322,6 +10687,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Non-eugenol surgical dressing and periodontal pack that has no burning sensation, no unpleasant taste, no disagreeable odor and offers proven protection to surgical sites. Extremely pliable and cohesive; ropes of any length or thickness can be formed. Sets with resilient, non-brittle hardness.</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9344,12 +10714,12 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.219750+00:00</t>
+          <t>2026-06-27T05:42:18.853142+00:00</t>
         </is>
       </c>
     </row>
@@ -9407,6 +10777,21 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Use in first aid treatment of: Bumps and Bruises, Sprains, Fractures, Minor Burns, Snake Bites, Insect Bites, Minor Bleeding, Nosebleeds, Headaches, Toothaches, Fever, Backaches, Sunstroke, Dislocations, Fatigue, Itching, Cramping, etc.
+Squeeze, Shake, Apply
+Instantly Cold
+FDA Approved
+Superior Quality
+Reaches therapeutic controlled temp every time
+Safe
+Time saving
+Provides maximum efficiency
+Non smear print
+Made in the USA</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9429,12 +10814,12 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.221967+00:00</t>
+          <t>2026-06-27T05:42:18.859112+00:00</t>
         </is>
       </c>
     </row>
@@ -9492,6 +10877,26 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Fully resorbable (16 weeks) purified porcine Type-I peritoneum membrane for osteogenesis during extraction socket preservation, ridge augmentation, periodontal defect repair or other grafting procedures.
+Common uses:
+Extraction ridge preservation.
+Periodontal defect repair.
+Vertical and horizontal ridge augmentation.
+Bone regeneration around teeth and implants.
+Sinus augmentation.
+Membrane technique utilizing tacks.
+&amp;nbsp;Features and benefits:
+Highly purified porcine peritoneum tissue.
+Excellent biocompatibility.
+Easily trimmed and adapted to defect site.
+Mechanically strong, yet drapable.
+Fully absorbable.
+Cell occlusive - inhibits undesired epithelial ingrowth.
+Can be tacked or sutured in place.</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9514,12 +10919,12 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.224308+00:00</t>
+          <t>2026-06-27T05:42:18.863985+00:00</t>
         </is>
       </c>
     </row>
@@ -9577,6 +10982,15 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Safe alternative to an autograft with no need for a second surgical site
+Osteoconductive
+Used for volumetric enhancement, space maintenance, and faster remodeling
+Sterile ground dental powder is available in cortical, cancellous and a cortical/cancellous mix.&amp;nbsp;
+Validated to a sterility assurance level (SAL) of 10(-6) in accordance with ISO 11137-2 Method 1.</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9599,12 +11013,12 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.226574+00:00</t>
+          <t>2026-06-27T05:42:18.868714+00:00</t>
         </is>
       </c>
     </row>
@@ -9662,6 +11076,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Sterile disposable scalpel; plastic handle with stainless steel blade.</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9684,12 +11103,12 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.228825+00:00</t>
+          <t>2026-06-27T05:42:18.873633+00:00</t>
         </is>
       </c>
     </row>
@@ -9747,6 +11166,16 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Sterile disposable scalpel with a stainless steel blade.&amp;nbsp;Intended for tissue separation, and other procedures that require a sharp surgical blade to puncture or cut.
+Offers the superior cutting advantages of stainless steel technology.
+Consistent sharpness, control and strength.
+Uniquely packaged for safety and ease of use.
+Sterile.
+Not made with natural rubber latex</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9769,12 +11198,12 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.231028+00:00</t>
+          <t>2026-06-27T05:42:18.878325+00:00</t>
         </is>
       </c>
     </row>
@@ -9832,6 +11261,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Sterile disposable scalpel; plastic handle with a stainless steel blade. Razor&amp;nbsp;sharp for superior cutting and a clean incision.</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9854,12 +11288,12 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.233290+00:00</t>
+          <t>2026-06-27T05:42:18.882793+00:00</t>
         </is>
       </c>
     </row>
@@ -9917,6 +11351,13 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Ethicon sutures are made of strong, sharp micrograin stainless steel. An exclusive Ethicon process yields the ideal balance between ductility and resistance to bending. Seamless swaging produces a needle diameter that closely matches the diameter&amp;nbsp;of the attached suture. A micro-thin, super-smooth finish allows the needle to&amp;nbsp;penetrate and pass through the tissue with an almost fluid-like flow.
+&amp;nbsp;
+For&amp;nbsp;Ethicon Sutures Chart along with additional information,&amp;nbsp;click here.</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr">
         <is>
           <t>{}</t>
@@ -9939,12 +11380,12 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.235494+00:00</t>
+          <t>2026-06-27T05:42:18.888866+00:00</t>
         </is>
       </c>
     </row>
@@ -10002,6 +11443,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Advanced instrument system of interchangeable blades and handles.
+Ultra-sharp, retains cutting efficiency.
+Ideal for microsurgery &amp;amp; use with a microscope.
+Optimal shapes &amp;amp; blade thickness.
+Small tips for surgical precision.
+Variety of applications including periodontal &amp;amp; regenerative surgery.
+Multiple handle designs.
+Made of high-quality stainless steel
+All blades are gamma-sterilized and can be used immediately after opening the package.&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10024,12 +11478,12 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.237674+00:00</t>
+          <t>2026-06-27T05:42:18.893276+00:00</t>
         </is>
       </c>
     </row>
@@ -10087,6 +11541,14 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>A collagen-based bone&amp;nbsp;augmentation material that&amp;nbsp;is placed into the socket&amp;nbsp;immediately following an&amp;nbsp;extraction to provide support&amp;nbsp;for implants, bridges, and&amp;nbsp;dentures.
+Promotes bone growth after tooth extraction, allowing implants to be placed in as early as 8 weeks.
+The surrounding&amp;nbsp;cells and capillaries gradually&amp;nbsp;infiltrate; as the extraction socket heals, it&amp;nbsp;becomes filled with new augmented bone.
+Easy-to-place, &amp;ldquo;bullet-shaped&amp;rdquo;&amp;nbsp;pellets are individually packaged in sterile containers.</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10109,12 +11571,12 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.240124+00:00</t>
+          <t>2026-06-27T05:42:18.897667+00:00</t>
         </is>
       </c>
     </row>
@@ -10172,6 +11634,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Synthetic particulate bone grafting material designed to be syringed directly into the bone defect.&amp;nbsp; Hardens into a stable, porous scaffold in approximately one minute, eliminating the need for a dental membrane in many cases.&amp;nbsp; Fully resorbable.</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10194,12 +11661,12 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.242373+00:00</t>
+          <t>2026-06-27T05:42:18.902578+00:00</t>
         </is>
       </c>
     </row>
@@ -10257,6 +11724,28 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>&amp;lt;p&amp;gt;White, porous, pliable and absorbable collagen wound dressing.&amp;lt;/p&amp;gt;
+&amp;lt;p&amp;gt;Common uses:&amp;lt;/p&amp;gt;
+&amp;lt;ul style="list-style-type: disc;"&amp;gt;
+&amp;lt;li&amp;gt;Extraction socket graft coverage.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Hemostasis.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;3&amp;lt;sup&amp;gt;rd&amp;lt;/sup&amp;gt; molar extractions.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Soft tissue repair.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Free-gingival graft donor sites.&amp;lt;/li&amp;gt;
+&amp;lt;/ul&amp;gt;
+&amp;lt;p&amp;gt;Features and benefits:&amp;lt;/p&amp;gt;
+&amp;lt;ul style="list-style-type: disc;"&amp;gt;
+&amp;lt;li&amp;gt;Highly purified Type I bovine collagen.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;High density for added resilience.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Easily trimmed according to clinical needs.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Fully absorbable.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Can easily be shaped by hand.&amp;lt;/li&amp;gt;
+&amp;lt;li&amp;gt;Individually packaged and sterile.&amp;lt;/li&amp;gt;
+&amp;lt;/ul&amp;gt;</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10279,12 +11768,12 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.244580+00:00</t>
+          <t>2026-06-27T05:42:18.907390+00:00</t>
         </is>
       </c>
     </row>
@@ -10342,6 +11831,15 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Please note: These products are on backorder with indefinite delivery. Safco&amp;nbsp;will not be accepting orders for these products until inventory is received.
+Absorbable collagen membranes made from purified bovine tendon.&amp;nbsp;Provides wound stabilization and creates space during guided tissue&amp;nbsp;regeneration where a longer&amp;nbsp;absorption rate is desired.&amp;nbsp;Material is pliable and does&amp;nbsp;not become slippery when&amp;nbsp;hydrated.
+Indicated for guided tissue regeneration procedures in periodontal defects to enhance regeneration of the periodontal apparatus. Sterile, individually packed (1 per box).
+HeliMend&amp;nbsp;&amp;ndash; Absorbs in 4 to 8 weeks.
+HeliMend Advanced &amp;ndash; Absorbs in 18 weeks.</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10364,12 +11862,12 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.246820+00:00</t>
+          <t>2026-06-27T05:42:18.912066+00:00</t>
         </is>
       </c>
     </row>
@@ -10427,6 +11925,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Hemostatic absorbable collagen material derived from bovine tendon. Promotes tissue growth by providing a scaffold-like structure. Its cylindrical shape is ideal for extraction and biopsy sites. Indicated for application to moist or bleeding oral wounds created during dental surgery to control bleeding and protect the surface of the wound from further injury. Absorbs within 10 to 14 days.</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10449,12 +11952,12 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.248903+00:00</t>
+          <t>2026-06-27T05:42:18.916556+00:00</t>
         </is>
       </c>
     </row>
@@ -10512,6 +12015,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Thin, soft, pliable collagen tape used for dressing minor wounds.&amp;nbsp; Tape accelerates wound healing and is absorbed into the body after 10 to 14 days.&amp;nbsp; Sterile and individually packaged.</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10534,12 +12042,12 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.251012+00:00</t>
+          <t>2026-06-27T05:42:18.921298+00:00</t>
         </is>
       </c>
     </row>
@@ -10597,6 +12105,12 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Topical hemostatic dressing in the form of a sterile fabric prepared by the chemical treatment of regenerated cellulose. Provides safe and effective control of bleeding for extractions and periodontal surgery.
+When the fabric comes into contact with blood or fluids, it expands and transforms to a clear, viscous gel which fills voids and seals capillary ends to help stop bleeding.</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10619,12 +12133,12 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.253278+00:00</t>
+          <t>2026-06-27T05:42:18.926311+00:00</t>
         </is>
       </c>
     </row>
@@ -10682,6 +12196,16 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>FDA-approved non-antibiotic cleanser and chemical desiccant that quickly eradicates biofilm from infected tissue surfaces without impacting healthy tissues. Safely debrides, coagulates, seals and reduces bleeding and pain, allowing the body to use its own defenses to promote natural healing.
+Antibiotic-free way to treat periodontal disease.
+Acts as a hemostatic.
+Flows easily into pits, furcations and deep pockets to effectively remove pathogens.
+Application takes seconds.
+Safe on dentin, enamel, porcelain and titanium.&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10704,12 +12228,12 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.255416+00:00</t>
+          <t>2026-06-27T05:42:18.930626+00:00</t>
         </is>
       </c>
     </row>
@@ -10767,6 +12291,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>SafeDay IV administration sets are indicated for 24-hour use. Components are not made with DEHP, latex or natural rubber. Sterile packaging permits direct placement of set on sterile field. Cost-effective needle-free access ports are designed to provide an effective barrier against microbial contamination.</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10789,12 +12318,12 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.262370+00:00</t>
+          <t>2026-06-27T05:42:18.945249+00:00</t>
         </is>
       </c>
     </row>
@@ -10852,6 +12381,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Flexible single use cold pack provides 20 minutes of therapy. Squeeze to activate; no need for refrigeration. Plastic outer wrap.</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10874,12 +12408,12 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.257774+00:00</t>
+          <t>2026-06-27T05:42:18.935859+00:00</t>
         </is>
       </c>
     </row>
@@ -10937,6 +12471,15 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Collagen Wound Dressing
+Integra Miltex absorbable collagen wound dressing products are used to help control bleeding and protect the wound site in order for the healing process to begin. For application to moist or bleeding clean oral wounds created during dental surgery, and to protect the surface of the wound from further injury. Collagen wound dressing products are reabsorbed by the body within 10 to 14 days after placement. These collagen products are packaged in individual clam shells with an easy-to-peel backing, making it easy for clinicians to open packages during procedures.
+Helps control bleeding
+10 to 14 day absorption
+Sterile, individually packaged dressings</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr">
         <is>
           <t>{}</t>
@@ -10959,12 +12502,12 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.260133+00:00</t>
+          <t>2026-06-27T05:42:18.940507+00:00</t>
         </is>
       </c>
     </row>
@@ -11022,6 +12565,13 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Due to supply chain disruptions, we are unable to accept backorders until the item is back in stock.
+Sterile, nonpyrogenic and contains no bacteriostatic or antimicrobial agents. Indicated for use in adults and pediatric patients as a source of electrolytes and water for hydration. EXCEL&amp;reg; IV bags feature a sturdy port system and are not manufactured with latex, PVC or DEHP.
+Click here to see full prescribing information</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11044,12 +12594,12 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.264646+00:00</t>
+          <t>2026-06-27T05:42:18.950241+00:00</t>
         </is>
       </c>
     </row>
@@ -11107,6 +12657,13 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Made by Surgical Specialties Corporation, with over 50 years suture manufacturing experience and over 25 years experience making stainless steel suture needles. ISO 9001 approved. All products meet or exceed FDA and QSR requirements and U.S.P. specifications. You get consistently sharp cutting needles plus&amp;nbsp;resistance to bending and breaking. All sizes are reverse cutting.
+&amp;nbsp;
+For&amp;nbsp;Look Sutures Chart&amp;nbsp;along with additional information,&amp;nbsp;click here.</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11129,12 +12686,12 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.266846+00:00</t>
+          <t>2026-06-27T05:42:18.955362+00:00</t>
         </is>
       </c>
     </row>
@@ -11192,6 +12749,16 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>GLASSVAN&amp;reg; Surgical Blades have been trusted by users around the world for more than 25 years.
+Automated grinding and proprietary polishing process ensure consistent, clean, and sharp cutting edges
+Produced from high quality Swiss carbon steel
+Two VCI strips ensure product and packaging integrity and reduce risk of blade piercing the foil
+Manufactured in FDA-inspected facilities and conform to ISO-7740 and ISO-13485
+Carbon steel and stainless-steel blades are available sterile in sizes 10-25, with select sizes also available non-sterile.</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11214,12 +12781,12 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.268957+00:00</t>
+          <t>2026-06-27T05:42:18.959992+00:00</t>
         </is>
       </c>
     </row>
@@ -11277,6 +12844,14 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>GLASSVAN&amp;reg; surgical blades have been trusted by users around the world for more than 25 years.
+Automated grinding and proprietary polishing process ensure consistent, clean, and sharp cutting edges
+Produced from high quality Swiss carbon steel.
+Two VCI strips ensure product and packaging integrity and reduce risk of blade piercing the foil.</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11299,12 +12874,12 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.271004+00:00</t>
+          <t>2026-06-27T05:42:18.965101+00:00</t>
         </is>
       </c>
     </row>
@@ -11362,6 +12937,19 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>RELI&amp;reg; PRO&amp;nbsp;sutures from MYCO Medical are premium sterile absorbable and non-absorbable surgical-grade sutures packaged in a new low-memory racetrack tray to improve suture performance
+All&amp;nbsp;RELI&amp;reg; PRO sutures include needles made from 300 Series stainless steel for the perfect blend of strength and ductility
+RediPass needle coating facilitates smoother needle penetration and reduces tissue dragging
+100% in-line manufacturing inspection ensures a smooth and secure needle to suture attachment site
+Pure Glide -- Continuous inner lined barrier eliminates any chance for the suture to get caught in gaps
+Notched Label -- Medical-grade paper label is notched in place to provide easy product identification and ensurable product integrity
+Easy Lift Needle -- The tab, when pressed from behind lifts the needle away from the card for easy removal
+Longer Lengths -- Longer suture lengths (up to 36") are available
+Twin Needle Parks -- Securely accommodates and protects all Myco needle configurations</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11384,12 +12972,12 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.273171+00:00</t>
+          <t>2026-06-27T05:42:18.969790+00:00</t>
         </is>
       </c>
     </row>
@@ -11447,6 +13035,16 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Non-slip, clear shield improves safety and enables easy blade size identification
+Ergonomic, non-slip plastic handle with integrated metric ruler for convenience
+Scalpel blades produced from high-quality Swiss stainless steel
+100% automated inspection verifies the blade to handle attachment
+Cold-staking used for attaching blade to handle, improving consistency
+Scalpels manufactured in facilities that conform to ISO 13485</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11469,12 +13067,12 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.275304+00:00</t>
+          <t>2026-06-27T05:42:18.974781+00:00</t>
         </is>
       </c>
     </row>
@@ -11532,6 +13130,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Non-medicated, clinically proven formula for relief from dry sockets and oral pain. Consists of essential oils and other natural ingredients. Place 8 to 10 drops onto a resorbable gelatin sponge or gauze strip directly to dry socket or areas of discomfort.</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11554,12 +13157,12 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.281038+00:00</t>
+          <t>2026-06-27T05:42:18.984825+00:00</t>
         </is>
       </c>
     </row>
@@ -11617,6 +13220,17 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Absorbable gelatin sponge hemostat, USP. Provides reliable and rapid hemostasis during dental surgical procedures.
+Offers fast and complete resorption in 3-7 days, no removal necessary. &amp;nbsp;
+Ideal size for easy application.
+Absorbs up to 35x its weight.
+Aids in control of hemorrhage in surgical or extraction sites.
+Individually packaged, sterile cubes prevent cross-contamination.
+Excellent carrier medium for fluids such as antibiotics or ORCA Dry Socket.</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11639,12 +13253,12 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.283334+00:00</t>
+          <t>2026-06-27T05:42:18.989848+00:00</t>
         </is>
       </c>
     </row>
@@ -11702,6 +13316,13 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Mineralized cancellous bone allograft Ideal for filling periodontal defects, extraction sockets, apicoectomy and root-resection. Can be used in conjunction with placement of dental implants. Double-sterile packaged jars can be taken directly to the sterile surgical site; material does not need to be transferred to another container.
+Mineralized cortical/cancellous bone allograftExcellent osteoconductive scaffold used in a variety of surgical procedures, including: extraction socket grafting, implant placement, osseous ridge repair, and sinus augmentations. Outstanding inner porosity and surface area, promotes clot formation and consistent, stable ossification and space maintenance. Double-sterile packaged jars; material does not need to be transferred to another container.
+Demineralized cancellous bone allograft sponge stripsPliable and resilient sponge matrix that can be adapted to numerous clinical needs including horizontal or vertical ridge augmentation, extraction sockets, recession defects, and can be used in conjunction with the placement of dental implants. Quickly becomes well vascularized following placement, and acts as an osteoconductive and osteoinductive scaffold for bone formation.</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11724,12 +13345,12 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.285639+00:00</t>
+          <t>2026-06-27T05:42:18.994273+00:00</t>
         </is>
       </c>
     </row>
@@ -11787,6 +13408,12 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Hydrogel dressing treats intraoral wounds and lesions. Provides fast, continuous pain relief without numbing. Protects from chemical and microbial contamination and promotes optimal healing.Contains no drugs, and has no toxicity or contraindications. Safe if swallowed. Individual 10g syringes are ideal for both in-office and take-home use. FDA approved.
+Please note:&amp;nbsp;SOCKIT! Gel has changed its name. This product has transitioned to OraSoothe "SOCKIT" Gel. The product&amp;nbsp;is the same&amp;nbsp;- only the name has changed.&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N134" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11809,12 +13436,12 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.277389+00:00</t>
+          <t>2026-06-27T05:42:18.979896+00:00</t>
         </is>
       </c>
     </row>
@@ -11872,6 +13499,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Ossify Bone Sheet is 100% laminar cortical bone that has been demineralized, which makes it flexible allowing it to be contoured, molded and trimmed. This enables it to be used as a membrane and can be screwed, tacked or sutured into place. It can be placed alone or in combination with particulate allograft to regenerate larger defects. It comes pre-hydrated and ready to use. &amp;nbsp; &amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11894,12 +13526,12 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.287807+00:00</t>
+          <t>2026-06-27T05:42:18.998844+00:00</t>
         </is>
       </c>
     </row>
@@ -11957,6 +13589,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Ossify DBM Fiber is a next generation bone allograft composed of interwoven demineralized cortical bone fibers. It is configured both by itself and with the addition of 1-1.5mm mineralized cancellous particles. This unique allograft provides an ideal scaffold for bone formation with its extremely high surface area and its optimum shape conforming properties, making it highly osteoconductive. In addition, it has great osteoinductive potential due to the specialized demineralized process. The graft hydrates very uniformly with PRP, blood or saline for maximum handling. It can be used in a variety of surgical applications, including socket grafting, GBR, sinus augmentation, and other bone grafting procedures.</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11979,12 +13616,12 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.290155+00:00</t>
+          <t>2026-06-27T05:42:19.003468+00:00</t>
         </is>
       </c>
     </row>
@@ -12042,6 +13679,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Ossify Min/Demin Cortical Cancellous Bone Allograft is a versatile, all-in-one bone graft designed to promote optimal bone regeneration across a wide range of clinical applications. Composed of a 50/50 blend of cortical and cancellous bone, the graft features 30% demineralized bone, leaving 70% of the material mineralized. This unique formulation enhances both osteoconductive and osteoinductive properties, supporting superior bone healing. Suitable for a variety of bone regeneration procedures, including socket grafting, ridge preservation, guided bone regeneration (GBR), and sinus augmentation. 0.5 &amp;ndash; 1.0mm particle size.&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12064,12 +13706,12 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.292224+00:00</t>
+          <t>2026-06-27T05:42:19.008110+00:00</t>
         </is>
       </c>
     </row>
@@ -12127,6 +13769,12 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Cyanoacrylate oral tissue adhesive used in dental surgeries. High viscosity formula provides increased control for precision application and less waste. Hemostatic and bacteriostatic. Violet color.
+Refrigeration required; this product is stored under refrigeration at Safco.</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12149,12 +13797,12 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.294717+00:00</t>
+          <t>2026-06-27T05:42:19.012970+00:00</t>
         </is>
       </c>
     </row>
@@ -12212,6 +13860,13 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Suture needles are made from Series 300 Stainless Steel, the ideal alloy for dental sutures. This alloy allows a very fine point geometry, stays sharp throughout the suturing procedure and is less likely to bend and more resistant to breakage. In addition, the needles have a&amp;nbsp;high-polished finish for a smoother penetration.
+&amp;nbsp;
+For Perma Sharp&amp;reg; Sutures Chart&amp;nbsp;along with additional information,&amp;nbsp;click here.</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12234,12 +13889,12 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.296893+00:00</t>
+          <t>2026-06-27T05:42:19.017670+00:00</t>
         </is>
       </c>
     </row>
@@ -12297,6 +13952,15 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Biocompatible Type I bovine Achilles tendon collagen. The absorbable, implantable material creates a barrier to protect PDL development from fast growing tissues. Supports wound stabilization and allows essential nutrients to pass through.
+Indicated for GTR procedures.
+Absorbable within 4-8 weeks.
+Appears white in the dry state; translucent and non-slippery when wet.
+Cut to size and shape.</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12319,12 +13983,12 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.299002+00:00</t>
+          <t>2026-06-27T05:42:19.022080+00:00</t>
         </is>
       </c>
     </row>
@@ -12382,6 +14046,14 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Sterile and fully resorbable synthetic bone grafting material. Ideal osteogenic matrix mimics human bone. Available in 2 biphasic&amp;nbsp;&amp;beta;-TCP (&amp;beta;-Tricalcium phosphate) / Hydroxyapatite formulations:
+40%/60%: New bone formation gradually forms at the same pace as natural bone.
+80%/20%: New natural bone will generate at an accelerated pace.
+Indications include: post-extraction socket preservation, periodontal defects, infrabony defects, peri-implant defects, sinus lift, ridge augmentation, and cystic cavities.</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12404,12 +14076,12 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.301014+00:00</t>
+          <t>2026-06-27T05:42:19.026456+00:00</t>
         </is>
       </c>
     </row>
@@ -12467,6 +14139,13 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Composed of 80% carbonate phosphate based mineral with a carbonate apatite structure combined with 20% Type I Achilles bovine tendon collagen. This mineral is physically and chemically comparable to the mineralized matrix of human bone, which makes it an excellent choice for socket preservation. No membrane needed in most cases. &amp;nbsp;
+Intended for use in dental surgery including:
+&amp;bull; Augmentation or reconstructive treatment of the alveolar ridge.&amp;bull; Filling of infrabony periodontal defects.&amp;bull; Filling of defects after root resection, apicoectomy, and cystectomy.&amp;bull; Filling of extraction sockets to enhance preservation of alveolar ridge.&amp;bull; Elevation of the maxillary sinus floor.&amp;bull; Filling of periodontal defects in conjunction with GTR. &amp;bull; Filling of peri-implant defects in conjunction with GBR.</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12489,12 +14168,12 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.303186+00:00</t>
+          <t>2026-06-27T05:42:19.031182+00:00</t>
         </is>
       </c>
     </row>
@@ -12552,6 +14231,15 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Extra sharp cutting edges on the needle reduce tissue drag and produce a precise, smooth penetration with minimal trauma. Needle channel is fitted to the specific size of the suture material. Excellent handling and tying characteristics. Reverse cutting.
+Plain gut (catgut): Made of first quality raw material, catgut has extremely high tensile strength. Every strand is precision polished to a uniform diameter, permitting smooth and secure knotting.
+Chromic gut (catgut): Produced with the same precision and quality materials as plain gut, plus treated with chromic acid salts to decrease tissue reactivity and provide a slower absorption rate.
+Black braided silk: Noncapillary silk has excellent handling and tying characteristics. Modern braiding technique provides a uniform smooth surface and a greater tensile strength.Nylon black monofilament: A non-absorbable polyamide suture with characteristic high tensile strength. The uniform smooth surface permits easy passage through tissue.
+For Safco SureStitch&amp;trade; Sutures Chart along with additional information,&amp;nbsp;click here.</t>
+        </is>
+      </c>
       <c r="N143" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12574,12 +14262,12 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.305462+00:00</t>
+          <t>2026-06-27T05:42:19.035561+00:00</t>
         </is>
       </c>
     </row>
@@ -12637,6 +14325,18 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Retractable blade scalpel offers ultimate safety.
+Sterile Stainless steel, razor-sharp cutting edge.
+Advance blade with slider in one motion.
+Blade locks into place with audible confirmation.
+Retract with one motion to protected position.
+Metric ruler on each scalpel.
+Individually packaged.
+&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="N144" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12659,12 +14359,12 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.307937+00:00</t>
+          <t>2026-06-27T05:42:19.039776+00:00</t>
         </is>
       </c>
     </row>
@@ -12722,6 +14422,14 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>The #3 style scalpel handle with metric ruler is used for cutting gingival tissue and making surgical incisions.
+The #5 Offset Angle Scalpel handle design is ideal for posterior and palatal areas with a 30 degree angle
+The #5 European Round Scalpel Blade Handle is used for cutting gingival tissue and making surgical incisions. The round scalpel handle provides greater rotational movement with fingertip control and enhances dexterity.&amp;nbsp;
+The #5 Straight Round Scalpel Blade Handle is used for cutting gingival tissue and making surgical incisions.</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12744,12 +14452,12 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.310268+00:00</t>
+          <t>2026-06-27T05:42:19.044392+00:00</t>
         </is>
       </c>
     </row>
@@ -12807,6 +14515,17 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Due to supply chain disruptions, we are unable to accept backorders until the item is back in stock.
+Indicated for extracellular fluid replacement, treatment of metabolic alkalosis in the presence of fluid loss and mild sodium depletion.
+Note:
+250ml bags and 500ml bags come in EXCEL&amp;reg; IV bags, which feature a sturdy port system.&amp;nbsp;
+1,000ml bags come in both E3 bags, which have rounded shoulders, no overwrap, a&amp;nbsp;seamless design, and the EXCEL&amp;reg;&amp;nbsp;IV bags, which feature a sturdy port system.
+Both the EXCEL&amp;reg; and E3 bags are&amp;nbsp;not manufactured with latex, PVC or DEHP.
+&amp;nbsp;Click here to see full prescribing information</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12829,12 +14548,12 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.312494+00:00</t>
+          <t>2026-06-27T05:42:19.048980+00:00</t>
         </is>
       </c>
     </row>
@@ -12892,6 +14611,12 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Due to supply chain disruptions, we are unable to accept backorders until the item is back in stock.
+0.9% sodium chloride injection. Viaflex IV injection plastic container. USP sterile disposable port closure. Not made with natural rubber latex.</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12914,12 +14639,12 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.314805+00:00</t>
+          <t>2026-06-27T05:42:19.053682+00:00</t>
         </is>
       </c>
     </row>
@@ -12977,6 +14702,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>FG bur designed for soft tissue surgery. Can be used as an alternative to electrosurgery and surgical blades; functions as a rotating scalpel for soft tissue that promotes coagulation for minimal bleeding. Biocompatible&amp;nbsp;hard oxide point cuts tissue without burning. Autoclavable.</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr">
         <is>
           <t>{}</t>
@@ -12999,12 +14729,12 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.316859+00:00</t>
+          <t>2026-06-27T05:42:19.058715+00:00</t>
         </is>
       </c>
     </row>
@@ -13062,6 +14792,13 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Due to supply chain disruptions, we are unable to accept backorders until the item is back in stock.
+Clear, colorless, odorless liquid. Sterile, hypotonic, nonpyrogenic, and contains no bacteriostatic or antimicrobial agents. EXCEL&amp;reg; IV bags feature a sturdy port system and are not manufactured with latex, PVC or DEHP.
+Click here to see full prescribing information</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13084,12 +14821,12 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.319101+00:00</t>
+          <t>2026-06-27T05:42:19.063752+00:00</t>
         </is>
       </c>
     </row>
@@ -13147,6 +14884,16 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Stainless steel. Handles are intended to be used for tissue separation, and other procedures that require a sharp surgical blade to puncture or cut.
+Consistent sharpness, control and strength surgeons demand.
+Uniquely packaged for safety and ease of use.
+Nonsterile.
+Sizes 3 fit blades sizes 10-15.
+Size 4 fits blade sizes 20-25.</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13169,12 +14916,12 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.321480+00:00</t>
+          <t>2026-06-27T05:42:19.068824+00:00</t>
         </is>
       </c>
     </row>
@@ -13232,6 +14979,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Box of 100 single-use blades,&amp;nbsp;in sterile foil packs.</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13254,12 +15006,12 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.323701+00:00</t>
+          <t>2026-06-27T05:42:19.073484+00:00</t>
         </is>
       </c>
     </row>
@@ -13317,6 +15069,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Single-use blades in individual foil packs.</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13339,12 +15096,12 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.325878+00:00</t>
+          <t>2026-06-27T05:42:19.078131+00:00</t>
         </is>
       </c>
     </row>
@@ -13402,6 +15159,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>The Hu-Friedy surgical blades are single use carbon steel blades used for cutting gingival tissue and making surgical incisions. They are crafted from the finest materials for strength and durability. Both microsurgical and standard styles are offered to match clinician and procedural preferences.</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13424,12 +15186,12 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.328311+00:00</t>
+          <t>2026-06-27T05:42:19.082564+00:00</t>
         </is>
       </c>
     </row>
@@ -13487,6 +15249,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Box of 100 sterile single-use&amp;nbsp;blades, in individual foil packs.</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13509,12 +15276,12 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.330539+00:00</t>
+          <t>2026-06-27T05:42:19.087044+00:00</t>
         </is>
       </c>
     </row>
@@ -13572,6 +15339,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Sterile, shear-weave, absorbable hemostat used to control bleeding in tooth extractions and oral surgery. Produced from oxidized&amp;nbsp;regenerated cellulose to ensure purity and consistency. Fully absorbable within 7-14 days. Strong yet flexible and malleable to conform to irregular&amp;nbsp;surfaces; may be folded or cut to size.</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13594,12 +15366,12 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.332838+00:00</t>
+          <t>2026-06-27T05:42:19.091616+00:00</t>
         </is>
       </c>
     </row>
@@ -13657,6 +15429,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Sterile, water insoluble, malleable porcine gelatin absorbable sponge, intended for hemostatic use by applying to a bleeding surface.</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13679,12 +15456,12 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.334931+00:00</t>
+          <t>2026-06-27T05:42:19.096078+00:00</t>
         </is>
       </c>
     </row>
@@ -13742,6 +15519,11 @@
           <t>in_stock</t>
         </is>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Miltex Regular Surgeon's Needles.</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr">
         <is>
           <t>{}</t>
@@ -13764,12 +15546,12 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>2026-06-27T05:36:53.337388+00:00</t>
+          <t>2026-06-27T05:42:19.100366+00:00</t>
         </is>
       </c>
     </row>
